--- a/data/trans_bre/DC-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/DC-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 10,44</t>
+          <t>2,89; 10,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,03; 17,27</t>
+          <t>9,99; 17,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,69; 14,59</t>
+          <t>6,95; 14,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,75; 25,48</t>
+          <t>16,15; 25,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,94; 40,66</t>
+          <t>9,83; 40,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,92; 112,09</t>
+          <t>50,47; 107,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,37; 104,91</t>
+          <t>38,61; 107,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>41,8; 80,62</t>
+          <t>42,41; 81,12</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,4; 13,58</t>
+          <t>7,96; 13,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,21; 13,85</t>
+          <t>9,26; 13,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,16; 10,29</t>
+          <t>6,05; 10,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,47; 40,01</t>
+          <t>15,65; 38,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>59,37; 116,91</t>
+          <t>54,61; 113,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>101,86; 193,28</t>
+          <t>101,6; 192,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,97; 152,9</t>
+          <t>71,17; 151,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>80,11; 281,97</t>
+          <t>81,46; 251,56</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 14,72</t>
+          <t>5,29; 14,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,4; 18,45</t>
+          <t>9,51; 18,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 8,54</t>
+          <t>1,38; 9,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,45; 20,91</t>
+          <t>12,32; 21,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,4; 149,14</t>
+          <t>35,69; 141,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>131,13; 530,77</t>
+          <t>134,82; 522,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,11; 134,11</t>
+          <t>12,57; 147,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>65,11; 146,04</t>
+          <t>64,01; 149,96</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,35; 12,38</t>
+          <t>8,41; 12,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,74; 15,23</t>
+          <t>11,78; 15,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 10,66</t>
+          <t>7,21; 10,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,98; 34,29</t>
+          <t>17,54; 32,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,37; 75,35</t>
+          <t>45,17; 74,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>103,7; 159,73</t>
+          <t>104,78; 161,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,89; 121,48</t>
+          <t>70,05; 121,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,93; 191,21</t>
+          <t>80,68; 188,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/DC-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/DC-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,61</t>
+          <t>22,17</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>67,39%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 10,48</t>
+          <t>2,84; 10,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,99; 17,12</t>
+          <t>9,99; 17,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,95; 14,86</t>
+          <t>6,82; 14,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,15; 25,26</t>
+          <t>17,69; 26,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 40,47</t>
+          <t>9,88; 41,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,47; 107,99</t>
+          <t>50,72; 113,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,61; 107,7</t>
+          <t>40,14; 106,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,41; 81,12</t>
+          <t>48,9; 88,19</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23,82</t>
+          <t>14,44</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>132,66%</t>
+          <t>72,22%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,96; 13,47</t>
+          <t>8,19; 13,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,26; 13,96</t>
+          <t>9,24; 13,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 10,27</t>
+          <t>6,27; 10,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,65; 38,71</t>
+          <t>11,97; 17,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,61; 113,64</t>
+          <t>57,37; 116,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>101,6; 192,66</t>
+          <t>100,66; 193,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,17; 151,97</t>
+          <t>73,68; 150,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>81,46; 251,56</t>
+          <t>55,97; 93,29</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,86</t>
+          <t>17,13</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>102,44%</t>
+          <t>104,24%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 14,53</t>
+          <t>5,05; 14,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,51; 18,49</t>
+          <t>9,57; 18,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 9,1</t>
+          <t>1,08; 8,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,32; 21,42</t>
+          <t>12,71; 21,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,69; 141,52</t>
+          <t>33,63; 133,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>134,82; 522,99</t>
+          <t>132,14; 496,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,57; 147,14</t>
+          <t>10,74; 138,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64,01; 149,96</t>
+          <t>67,56; 149,07</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,85</t>
+          <t>17,41</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>113,56%</t>
+          <t>81,41%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,41; 12,31</t>
+          <t>8,42; 12,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,78; 15,6</t>
+          <t>11,83; 15,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 10,66</t>
+          <t>7,05; 10,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,54; 32,76</t>
+          <t>15,45; 19,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,17; 74,5</t>
+          <t>45,86; 73,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>104,78; 161,59</t>
+          <t>106,34; 159,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,05; 121,73</t>
+          <t>69,8; 122,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>80,68; 188,97</t>
+          <t>67,94; 97,43</t>
         </is>
       </c>
     </row>
